--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk10pct_wu300000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk10pct_wu300000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22505</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>29424</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>57012</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>69797</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>73068</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>60280</t>
+          <t>29422</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49394</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
